--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487571_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487571_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.3885</v>
+        <v>7.0548</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9787</v>
+        <v>6.6716</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4098</v>
+        <v>0.3831</v>
       </c>
       <c r="G2" t="n">
         <v>1.3583</v>
@@ -610,13 +610,13 @@
         <v>1.7626</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6468</v>
+        <v>0.313</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.2258</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1139</v>
+        <v>0.0872</v>
       </c>
       <c r="V2" t="n">
         <v>4.6001</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. NIETO GONZALEZ</t>
+          <t>C. MONTERO MECA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2822</v>
+        <v>0.4903</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7885</v>
+        <v>0.8055</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5063</v>
+        <v>-0.3152</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.287</v>
+        <v>1.8558</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.5043</v>
+        <v>-1.3678</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7827</v>
+        <v>3.2236</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.0203</v>
+        <v>3.5839</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.621</v>
+        <v>0.9424</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.3993</v>
+        <v>2.6414</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2667</v>
+        <v>-1.7281</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8833</v>
+        <v>-2.3102</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3834</v>
+        <v>0.5821</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1751</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1751</v>
+        <v>1.7626</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1775</v>
+        <v>-0.2949</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5921999999999999</v>
+        <v>-0.487</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4148</v>
+        <v>0.192</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2166</v>
+        <v>-0.8747</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2166</v>
+        <v>-0.3329</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.5417</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. CZERAPOWIC</t>
+          <t>J. NIETO GONZALEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2203</v>
+        <v>0.0927</v>
       </c>
       <c r="E4" t="n">
-        <v>0.611</v>
+        <v>0.4386</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8314</v>
+        <v>-0.3459</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1792</v>
+        <v>-2.287</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.1092</v>
+        <v>-1.5043</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2885</v>
+        <v>-0.7827</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2511</v>
+        <v>-1.0203</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2739</v>
+        <v>-0.621</v>
       </c>
       <c r="L4" t="n">
-        <v>2.525</v>
+        <v>-0.3993</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0718</v>
+        <v>-1.2667</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.8353</v>
+        <v>-0.8833</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2366</v>
+        <v>-0.3834</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1958</v>
+        <v>1.1751</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7626</v>
+        <v>1.1751</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8786</v>
+        <v>-0.0121</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5652</v>
+        <v>0.2423</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3134</v>
+        <v>-0.2544</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6749000000000001</v>
+        <v>1.2166</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8837</v>
+        <v>1.2166</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2088</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. MONTERO MECA</t>
+          <t>E. CZERAPOWIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2228</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.175</v>
+        <v>0.7134</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0478</v>
+        <v>-0.6443</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8558</v>
+        <v>0.1792</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.3678</v>
+        <v>-2.1092</v>
       </c>
       <c r="I5" t="n">
-        <v>3.2236</v>
+        <v>2.2885</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5839</v>
+        <v>2.2511</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9424</v>
+        <v>-0.2739</v>
       </c>
       <c r="L5" t="n">
-        <v>2.6414</v>
+        <v>2.525</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.7281</v>
+        <v>-2.0718</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.3102</v>
+        <v>-1.8353</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5821</v>
+        <v>-0.2366</v>
       </c>
       <c r="P5" t="n">
         <v>-0.1958</v>
@@ -844,22 +844,22 @@
         <v>1.7626</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0081</v>
+        <v>-0.5891999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.4674</v>
+        <v>-0.4629</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4593</v>
+        <v>-0.1263</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.8747</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3329</v>
+        <v>0.8837</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5417</v>
+        <v>-0.2088</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9429999999999999</v>
+        <v>-0.5849</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2951</v>
+        <v>0.2522</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2381</v>
+        <v>-0.8371</v>
       </c>
       <c r="G6" t="n">
         <v>-1.3215</v>
@@ -922,13 +922,13 @@
         <v>2.1543</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9207</v>
+        <v>-0.5627</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3405</v>
+        <v>-0.3835</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5802</v>
+        <v>-0.1792</v>
       </c>
       <c r="V6" t="n">
         <v>0.1242</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. IGLESIAS GONZALEZ</t>
+          <t>A. VAZQUEZ ABAD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.2506</v>
+        <v>-2.9209</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.7272</v>
+        <v>-2.3802</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5235</v>
+        <v>-0.5407</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.1889</v>
+        <v>-2.2932</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7329</v>
+        <v>-0.7574</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.4561</v>
+        <v>-1.5358</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.3785</v>
+        <v>-1.2922</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6941000000000001</v>
+        <v>-0.6908</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.0727</v>
+        <v>-0.6014</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.8104</v>
+        <v>-1.001</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.427</v>
+        <v>-0.0667</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3834</v>
+        <v>-0.9344</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1958</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7834</v>
+        <v>0.1958</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4095</v>
+        <v>0.1557</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3694</v>
+        <v>-0.1088</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7789</v>
+        <v>0.2645</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. VAZQUEZ ABAD</t>
+          <t>C. IGLESIAS GONZALEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.4685</v>
+        <v>-3.6959</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.6872</v>
+        <v>-2.9318</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7812</v>
+        <v>-0.764</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.2932</v>
+        <v>-3.1889</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7574</v>
+        <v>-0.7329</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.5358</v>
+        <v>-2.4561</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.2922</v>
+        <v>-1.3785</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6908</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6014</v>
+        <v>-2.0727</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.001</v>
+        <v>-1.8104</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0667</v>
+        <v>-1.427</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9344</v>
+        <v>-0.3834</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7834</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1958</v>
+        <v>0.7834</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3919</v>
+        <v>-0.0357</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4158</v>
+        <v>-0.574</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0239</v>
+        <v>0.5383</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.8943</v>
+        <v>-5.8102</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8095</v>
+        <v>-2.0571</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.0848</v>
+        <v>-3.7531</v>
       </c>
       <c r="G9" t="n">
         <v>-4.2517</v>
@@ -1156,13 +1156,13 @@
         <v>0.5875</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6237</v>
+        <v>-0.2922</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5476</v>
+        <v>-0.7952</v>
       </c>
       <c r="U9" t="n">
-        <v>1.1713</v>
+        <v>0.503</v>
       </c>
       <c r="V9" t="n">
         <v>-0.8747</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-11.1468</v>
+        <v>-10.8735</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.6101</v>
+        <v>-6.5507</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.5367</v>
+        <v>-4.3228</v>
       </c>
       <c r="G10" t="n">
         <v>-6.029</v>
@@ -1234,13 +1234,13 @@
         <v>0.5875</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1225</v>
+        <v>-0.8493000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9922</v>
+        <v>-0.9328</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1303</v>
+        <v>0.0835</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6659</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-16.4756</v>
+        <v>-16.1785</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.335699999999998</v>
+        <v>-5.038499999999999</v>
       </c>
       <c r="F11" t="n">
         <v>-11.14</v>
@@ -1288,7 +1288,7 @@
         <v>4.782</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3644999999999998</v>
+        <v>-0.3645</v>
       </c>
       <c r="L11" t="n">
         <v>5.146399999999999</v>
@@ -1300,7 +1300,7 @@
         <v>-12.9105</v>
       </c>
       <c r="O11" t="n">
-        <v>-7.849499999999999</v>
+        <v>-7.849500000000001</v>
       </c>
       <c r="P11" t="n">
         <v>-1.9583</v>
@@ -1312,10 +1312,10 @@
         <v>10.7714</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.4643</v>
+        <v>-2.1674</v>
       </c>
       <c r="T11" t="n">
-        <v>-3.5731</v>
+        <v>-3.2761</v>
       </c>
       <c r="U11" t="n">
         <v>1.1086</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.313499999999999</v>
+        <v>8.6693</v>
       </c>
       <c r="E12" t="n">
-        <v>4.8153</v>
+        <v>5.2246</v>
       </c>
       <c r="F12" t="n">
-        <v>3.4982</v>
+        <v>3.4447</v>
       </c>
       <c r="G12" t="n">
         <v>6.3223</v>
@@ -1390,13 +1390,13 @@
         <v>0.9792</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7366</v>
+        <v>1.0925</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4752</v>
+        <v>-0.0659</v>
       </c>
       <c r="U12" t="n">
-        <v>1.2118</v>
+        <v>1.1583</v>
       </c>
       <c r="V12" t="n">
         <v>0.2754</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. FILGUEIRA BUCETA</t>
+          <t>H. REY PEREZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.1804</v>
+        <v>5.0324</v>
       </c>
       <c r="E13" t="n">
-        <v>3.38</v>
+        <v>3.5457</v>
       </c>
       <c r="F13" t="n">
-        <v>2.8004</v>
+        <v>1.4867</v>
       </c>
       <c r="G13" t="n">
-        <v>2.3849</v>
+        <v>2.4909</v>
       </c>
       <c r="H13" t="n">
-        <v>3.0868</v>
+        <v>-0.505</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7019</v>
+        <v>2.9959</v>
       </c>
       <c r="J13" t="n">
-        <v>1.6736</v>
+        <v>3.1962</v>
       </c>
       <c r="K13" t="n">
-        <v>2.6744</v>
+        <v>-0.5768</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.0007</v>
+        <v>3.7731</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7113</v>
+        <v>-0.7053</v>
       </c>
       <c r="N13" t="n">
-        <v>0.4125</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2988</v>
+        <v>-0.7772</v>
       </c>
       <c r="P13" t="n">
-        <v>1.7626</v>
+        <v>1.5668</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.7626</v>
+        <v>1.5668</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8204</v>
+        <v>0.488</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1557</v>
+        <v>0.0741</v>
       </c>
       <c r="U13" t="n">
-        <v>1.6647</v>
+        <v>0.4139</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.7875</v>
+        <v>0.4866</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5507</v>
+        <v>0.2754</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.3383</v>
+        <v>0.2113</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>H. REY PEREZ</t>
+          <t>A. FILGUEIRA BUCETA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.4695</v>
+        <v>4.4381</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4667</v>
+        <v>2.3567</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0027</v>
+        <v>2.0814</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4909</v>
+        <v>2.3849</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.505</v>
+        <v>3.0868</v>
       </c>
       <c r="I14" t="n">
-        <v>2.9959</v>
+        <v>-0.7019</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1962</v>
+        <v>1.6736</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.5768</v>
+        <v>2.6744</v>
       </c>
       <c r="L14" t="n">
-        <v>3.7731</v>
+        <v>-1.0007</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7053</v>
+        <v>0.7113</v>
       </c>
       <c r="N14" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.4125</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.7772</v>
+        <v>0.2988</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5668</v>
+        <v>1.7626</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5668</v>
+        <v>1.7626</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9251</v>
+        <v>1.0781</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9951</v>
+        <v>0.1323</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.9457</v>
       </c>
       <c r="V14" t="n">
-        <v>0.4866</v>
+        <v>-0.7875</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2754</v>
+        <v>0.5507</v>
       </c>
       <c r="X14" t="n">
-        <v>0.2113</v>
+        <v>-1.3383</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8439</v>
+        <v>2.6217</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1164</v>
+        <v>1.7071</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7275</v>
+        <v>0.9146</v>
       </c>
       <c r="G15" t="n">
         <v>2.4311</v>
@@ -1624,13 +1624,13 @@
         <v>0.1958</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4923</v>
+        <v>0.2701</v>
       </c>
       <c r="T15" t="n">
-        <v>0.504</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0117</v>
+        <v>0.1754</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2754</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2201</v>
+        <v>2.4202</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6431</v>
+        <v>-0.3361</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8632</v>
+        <v>2.7563</v>
       </c>
       <c r="G16" t="n">
         <v>2.4207</v>
@@ -1702,13 +1702,13 @@
         <v>0.7834</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6415</v>
+        <v>0.8416</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4752</v>
+        <v>-0.1682</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1168</v>
+        <v>1.0098</v>
       </c>
       <c r="V16" t="n">
         <v>0.3329</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8259</v>
+        <v>2.2786</v>
       </c>
       <c r="E17" t="n">
-        <v>1.41</v>
+        <v>1.5123</v>
       </c>
       <c r="F17" t="n">
-        <v>0.416</v>
+        <v>0.7663</v>
       </c>
       <c r="G17" t="n">
         <v>1.5887</v>
@@ -1780,13 +1780,13 @@
         <v>1.7626</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5461</v>
+        <v>-0.0935</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.387</v>
+        <v>-0.2847</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1591</v>
+        <v>0.1911</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. HOGAN</t>
+          <t>A. BOUZAN CUMPLIDO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1448</v>
+        <v>0.6042</v>
       </c>
       <c r="E18" t="n">
-        <v>3.7628</v>
+        <v>1.3995</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.6181</v>
+        <v>-0.7953</v>
       </c>
       <c r="G18" t="n">
-        <v>2.2624</v>
+        <v>1.8461</v>
       </c>
       <c r="H18" t="n">
-        <v>3.1912</v>
+        <v>-0.5780999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9288</v>
+        <v>2.4242</v>
       </c>
       <c r="J18" t="n">
-        <v>3.5833</v>
+        <v>2.7669</v>
       </c>
       <c r="K18" t="n">
-        <v>3.462</v>
+        <v>-0.1719</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1212</v>
+        <v>2.9388</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3209</v>
+        <v>-0.9209000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2708</v>
+        <v>-0.4062</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0501</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1958</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7834</v>
+        <v>0.9792</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9671999999999999</v>
+        <v>-0.0253</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5505</v>
+        <v>-0.3882</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4167</v>
+        <v>0.3629</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.889</v>
+        <v>-1.2166</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6083</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.4973</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. BOUZAN CUMPLIDO</t>
+          <t>D. HOGAN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.267</v>
+        <v>0.4994</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0925</v>
+        <v>3.2511</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3595</v>
+        <v>-2.7517</v>
       </c>
       <c r="G19" t="n">
-        <v>1.8461</v>
+        <v>2.2624</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5780999999999999</v>
+        <v>3.1912</v>
       </c>
       <c r="I19" t="n">
-        <v>2.4242</v>
+        <v>-0.9288</v>
       </c>
       <c r="J19" t="n">
-        <v>2.7669</v>
+        <v>3.5833</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1719</v>
+        <v>3.462</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9388</v>
+        <v>0.1212</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9209000000000001</v>
+        <v>-1.3209</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4062</v>
+        <v>-0.2708</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-1.0501</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9792</v>
+        <v>0.7834</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8964</v>
+        <v>0.3219</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6952</v>
+        <v>0.0388</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2013</v>
+        <v>0.283</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2166</v>
+        <v>-1.889</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.6083</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2166</v>
+        <v>-2.4973</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1236</v>
+        <v>-0.8046</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5449000000000001</v>
+        <v>-0.4426</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5787</v>
+        <v>-0.3621</v>
       </c>
       <c r="G20" t="n">
         <v>0.6843</v>
@@ -2014,13 +2014,13 @@
         <v>0.7834</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9081</v>
+        <v>-0.5891999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4158</v>
+        <v>-0.3135</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4923</v>
+        <v>-0.2757</v>
       </c>
       <c r="V20" t="n">
         <v>0.2754</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0231</v>
+        <v>-3.1418</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9694</v>
+        <v>-1.3554</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.0537</v>
+        <v>-1.7864</v>
       </c>
       <c r="G21" t="n">
         <v>-2.037</v>
@@ -2092,13 +2092,13 @@
         <v>0.9792</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5315</v>
+        <v>-0.6502</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7546</v>
+        <v>-0.1406</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7769</v>
+        <v>-0.5096000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>-0.4546</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.1087</v>
+        <v>-5.4596</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.7464</v>
+        <v>-5.723</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6375999999999999</v>
+        <v>0.2634</v>
       </c>
       <c r="G22" t="n">
         <v>-4.4164</v>
@@ -2170,13 +2170,13 @@
         <v>2.1543</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2365</v>
+        <v>0.4126</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.111</v>
+        <v>-0.0876</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8744</v>
+        <v>0.5002</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6724</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>16.4757</v>
+        <v>17.1579</v>
       </c>
       <c r="E23" t="n">
         <v>11.1399</v>
       </c>
       <c r="F23" t="n">
-        <v>5.335600000000001</v>
+        <v>6.0179</v>
       </c>
       <c r="G23" t="n">
         <v>15.97800000000001</v>
@@ -2239,7 +2239,7 @@
         <v>-5.1465</v>
       </c>
       <c r="P23" t="n">
-        <v>1.958400000000001</v>
+        <v>1.9584</v>
       </c>
       <c r="Q23" t="n">
         <v>-10.7715</v>
@@ -2248,13 +2248,13 @@
         <v>12.7299</v>
       </c>
       <c r="S23" t="n">
-        <v>2.4645</v>
+        <v>3.1466</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1087</v>
+        <v>-1.1088</v>
       </c>
       <c r="U23" t="n">
-        <v>3.5731</v>
+        <v>4.255000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-3.9252</v>
